--- a/tp_education_system/backend/exports/绩效工资审批表_2026年5月.xlsx
+++ b/tp_education_system/backend/exports/绩效工资审批表_2026年5月.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绩效工资审批表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'绩效工资审批表'!$A$1:$F$31</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -27,12 +29,12 @@
     </font>
     <font>
       <name val="宋体"/>
-      <b val="1"/>
-      <sz val="16"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -48,7 +50,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -56,6 +58,7 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="00000000"/>
@@ -103,30 +106,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -492,17 +509,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14.28571428571429" customWidth="1" min="2" max="2"/>
-    <col width="14.28571428571429" customWidth="1" min="3" max="3"/>
-    <col width="14.28571428571429" customWidth="1" min="4" max="4"/>
-    <col width="10.71428571428571" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="11.2" customWidth="1" min="1" max="1"/>
+    <col width="13.33" customWidth="1" min="2" max="2"/>
+    <col width="13.33" customWidth="1" min="3" max="3"/>
+    <col width="13.33" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="27" customHeight="1">
@@ -513,156 +530,156 @@
       </c>
     </row>
     <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>填报单位： 太平镇中心学校 填报时间: 2026年4月30日 单位： 人、元</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>填报单位： 太平镇中心学校 填报时间: 2026年5月1日 单位： 人、元</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>呈报单位意见</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>据实填写，同意呈报。（盖章）2026年4月30日</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>据实填写，同意呈报。（盖章）2026年5月1日</t>
         </is>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="5" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="A4" s="4" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>行政管理人员</t>
         </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="5" t="n"/>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="A5" s="4" t="n"/>
+      <c r="C5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="C6" s="4" t="inlineStr"/>
+      <c r="A6" s="4" t="n"/>
+      <c r="C6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="5" t="n"/>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="A7" s="4" t="n"/>
+      <c r="C7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="C8" s="4" t="inlineStr"/>
+      <c r="A8" s="4" t="n"/>
+      <c r="C8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="7" t="n"/>
-      <c r="C9" s="4" t="inlineStr"/>
+      <c r="C9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>专业技术人员</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>教育局意见</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>（盖章）2026年5月1日</t>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>（盖章）2026年5月2日</t>
         </is>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="4" t="inlineStr"/>
+      <c r="A11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="4" t="inlineStr"/>
+      <c r="A12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="4" t="inlineStr"/>
+      <c r="A13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="4" t="inlineStr"/>
+      <c r="A14" s="6" t="inlineStr"/>
     </row>
     <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="4" t="inlineStr"/>
+      <c r="A15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>工人</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="4" t="inlineStr"/>
+      <c r="A17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="4" t="inlineStr"/>
+      <c r="A18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>人事部门意见</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>根据相关文件及有关规定，经审核，同意你单位：基础性绩效工资50人，65000元；生活补贴50人，65000元；合计50人，65000元；岗位设置遗留50人，65000元；总计50人，65000元。无乡镇补贴5人，张三、李四、王五。2026年5月1日</t>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>根据相关文件及有关规定，经审核，同意你单位：基础性绩效工资50人，65000元；生活补贴50人，65000元；合计50人，65000元；岗位设置遗留50人，65000元；总计50人，65000元。无乡镇补贴5人，张三、李四、王五。2026年5月2日</t>
         </is>
       </c>
     </row>
     <row r="20" ht="25" customHeight="1">
-      <c r="A20" s="5" t="n"/>
-      <c r="C20" s="4" t="inlineStr"/>
+      <c r="A20" s="4" t="n"/>
+      <c r="C20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="5" t="n"/>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="A21" s="4" t="n"/>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>1106</t>
         </is>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="5" t="n"/>
-      <c r="C22" s="4" t="inlineStr"/>
+      <c r="A22" s="4" t="n"/>
+      <c r="C22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="5" t="n"/>
-      <c r="C23" s="4" t="inlineStr"/>
+      <c r="A23" s="4" t="n"/>
+      <c r="C23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="5" t="n"/>
-      <c r="C24" s="4" t="inlineStr"/>
+      <c r="A24" s="4" t="n"/>
+      <c r="C24" s="6" t="inlineStr"/>
     </row>
     <row r="25" ht="37" customHeight="1">
-      <c r="A25" s="5" t="n"/>
-      <c r="C25" s="4" t="inlineStr"/>
+      <c r="A25" s="4" t="n"/>
+      <c r="C25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="37" customHeight="1">
-      <c r="A26" s="5" t="n"/>
-      <c r="C26" s="4" t="inlineStr"/>
+      <c r="A26" s="4" t="n"/>
+      <c r="C26" s="6" t="inlineStr"/>
     </row>
     <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="5" t="n"/>
-      <c r="C27" s="4" t="inlineStr"/>
+      <c r="A27" s="4" t="n"/>
+      <c r="C27" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="25" customHeight="1">
-      <c r="A28" s="5" t="n"/>
-      <c r="C28" s="4" t="inlineStr"/>
+      <c r="A28" s="4" t="n"/>
+      <c r="C28" s="6" t="inlineStr"/>
     </row>
     <row r="29" ht="25" customHeight="1">
-      <c r="A29" s="5" t="n"/>
-      <c r="C29" s="4" t="inlineStr"/>
+      <c r="A29" s="4" t="n"/>
+      <c r="C29" s="6" t="inlineStr"/>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="7" t="n"/>
-      <c r="C30" s="4" t="inlineStr"/>
+      <c r="C30" s="6" t="inlineStr"/>
     </row>
     <row r="31" ht="35" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
@@ -687,6 +704,6 @@
     <mergeCell ref="E10:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0" firstPageNumber="1"/>
 </worksheet>
 </file>
--- a/tp_education_system/backend/exports/绩效工资审批表_2026年5月.xlsx
+++ b/tp_education_system/backend/exports/绩效工资审批表_2026年5月.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绩效工资审批表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'绩效工资审批表'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'绩效工资审批表'!$A$1:$F$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,12 +29,12 @@
     </font>
     <font>
       <name val="宋体"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="宋体"/>
-      <b val="1"/>
-      <sz val="16"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -50,7 +50,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -58,7 +58,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
     <border>
       <left style="thin">
         <color rgb="00000000"/>
@@ -73,78 +72,29 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -511,178 +461,458 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.2" customWidth="1" min="1" max="1"/>
-    <col width="13.33" customWidth="1" min="2" max="2"/>
-    <col width="13.33" customWidth="1" min="3" max="3"/>
-    <col width="13.33" customWidth="1" min="4" max="4"/>
+    <col width="13.33333333333333" customWidth="1" min="2" max="2"/>
+    <col width="13.33333333333333" customWidth="1" min="3" max="3"/>
+    <col width="13.33333333333333" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>2026年5月 义务教育学校教职工绩效工资审批表</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>填报单位： 太平镇中心学校 填报时间: 2026年5月1日 单位： 人、元</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>填报单位： 太平中心学校 填报时间: 2026年5月1日 单位： 人、元</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>小计</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>呈报单位意见</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>据实填写，同意呈报。（盖章）2026年5月1日</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="4" t="n"/>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>据实填写，同意呈报。（盖章）2026年4月28日</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>行政管理人员</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="4" t="n"/>
-      <c r="C5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="4" t="n"/>
-      <c r="C6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="C7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="4" t="n"/>
-      <c r="C8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="7" t="n"/>
-      <c r="C9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1、副处级</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2、正科级</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>3、副科级</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>17600</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>4、科员级</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>5、办事员级</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>专业技术人员</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>教育局意见</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>（盖章）2026年5月2日</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16" ht="25" customHeight="1">
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>1、正高级</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3800</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2、高级教师</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>3、一级教师</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>4、二级教师</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>17600</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>5、三级教师</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>工人</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>人事部门意见</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>根据相关文件及有关规定，经审核，同意你单位：基础性绩效工资50人，65000元；生活补贴50人，65000元；合计50人，65000元；岗位设置遗留50人，65000元；总计50人，65000元。无乡镇补贴5人，张三、李四、王五。2026年5月2日</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1">
-      <c r="A20" s="4" t="n"/>
-      <c r="C20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="4" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="4" t="n"/>
-      <c r="C22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="4" t="n"/>
-      <c r="C23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="4" t="n"/>
-      <c r="C24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="37" customHeight="1">
-      <c r="A25" s="4" t="n"/>
-      <c r="C25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="37" customHeight="1">
-      <c r="A26" s="4" t="n"/>
-      <c r="C26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="4" t="n"/>
-      <c r="C27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28" ht="25" customHeight="1">
-      <c r="A28" s="4" t="n"/>
-      <c r="C28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29" ht="25" customHeight="1">
-      <c r="A29" s="4" t="n"/>
-      <c r="C29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="25" customHeight="1">
-      <c r="A30" s="7" t="n"/>
-      <c r="C30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31" ht="35" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>1、高级技师</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2、技师</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>3、高级工</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>4、中级工</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>5、初级工</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>6、普工</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>绩效工资合计</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>乡镇补贴合计</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>15750</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>岗位设置遗留问题</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>张老师</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>岗位设置遗留问题</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>李老师</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>岗位设置遗留问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>岗位设置遗留问题合计</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>退休干部</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>退休工人</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>离休干部</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>备注：</t>
         </is>
@@ -691,17 +921,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="F10:F18"/>
-    <mergeCell ref="B19:B30"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="F17:F31"/>
+    <mergeCell ref="E17:E31"/>
+    <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="A19:A30"/>
-    <mergeCell ref="E10:E18"/>
+    <mergeCell ref="E3:E9"/>
+    <mergeCell ref="F3:F9"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="F11:F19"/>
+    <mergeCell ref="E11:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0" firstPageNumber="1"/>

--- a/tp_education_system/backend/exports/绩效工资审批表_2026年5月.xlsx
+++ b/tp_education_system/backend/exports/绩效工资审批表_2026年5月.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绩效工资审批表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'绩效工资审批表'!$A$1:$F$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet1'!$A$1:$K$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -76,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -93,8 +93,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -461,159 +464,210 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.2" customWidth="1" min="1" max="1"/>
-    <col width="13.33333333333333" customWidth="1" min="2" max="2"/>
-    <col width="13.33333333333333" customWidth="1" min="3" max="3"/>
-    <col width="13.33333333333333" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13.82" customWidth="1" min="1" max="1"/>
+    <col width="7.64" customWidth="1" min="2" max="2"/>
+    <col width="13.04" customWidth="1" min="3" max="3"/>
+    <col width="9.359999999999999" customWidth="1" min="4" max="4"/>
+    <col width="6.09" customWidth="1" min="5" max="5"/>
+    <col width="8.82" customWidth="1" min="6" max="6"/>
+    <col width="17.64" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="3.91" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="8.640000000000001" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="27" customHeight="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2026年5月 义务教育学校教职工绩效工资审批表</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>填报单位： 太平中心学校 填报时间: 2026年5月1日 单位： 人、元</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>填报单位：</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>太平镇中心学校</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>填报时间:</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>单位：</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>人、元</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>项  目</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>基础性工资</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>呈报单位意见</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>人数</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>月工资标准</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>呈报单位意见</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>据实填写，同意呈报。（盖章）2026年4月28日</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>行政管理人员</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>1、副处级</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C6" s="5" t="n">
         <v>3500</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D6" s="5" t="n">
         <v>10500</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>据实填写，同意呈报。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2、正科级</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C7" s="5" t="n">
         <v>2800</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D7" s="5" t="n">
         <v>14000</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>（盖章）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>3、副科级</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B8" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C8" s="5" t="n">
         <v>2200</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D8" s="5" t="n">
         <v>17600</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>4、科员级</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>21600</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="B9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1185</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5925</v>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>5、办事员级</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
+      <c r="B10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1106</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>专业技术人员</t>
         </is>
       </c>
-    </row>
-    <row r="12">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>教育局意见</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>1、正高级</t>
@@ -623,84 +677,84 @@
         <v>2</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3800</v>
+        <v>1862</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>7600</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>2、高级教师</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>3200</v>
+        <v>1523</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>67012</v>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>3、一级教师</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>2600</v>
+        <v>1309</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>39000</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>178024</v>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>4、二级教师</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2200</v>
+        <v>1241</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>17600</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>186150</v>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>5、三级教师</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1800</v>
+        <v>1128</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>5400</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>21432</v>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>工人</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="25" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>1、高级技师</t>
@@ -710,13 +764,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>2800</v>
+        <v>1331</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>2800</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>2、技师</t>
@@ -726,212 +780,279 @@
         <v>2</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2400</v>
+        <v>1331</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>3、高级工</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1219</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3657</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>人事部门意见</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    根据相关文件及有关规定，经审核，同意你单位：</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>4、中级工</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C20" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>4、中级工</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="C21" s="5" t="n">
-        <v>1800</v>
+        <v>1185</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>5400</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>5925</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>基础性绩效工资</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>357</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>462311</v>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>5、初级工</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1106</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>生活补贴</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>356</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>124600</v>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>6、普工</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1106</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>合计：</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>586911</v>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>绩效工资合计</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>357</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>462311</v>
+      </c>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>乡镇补贴合计</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>356</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>124600</v>
+      </c>
+    </row>
+    <row r="26" ht="37" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>岗位设置
+遗留问题</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>李发金</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>321.3</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>321.3</v>
+      </c>
+    </row>
+    <row r="27" ht="37" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>岗位设置
+遗留问题</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>张照凯</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>353.94</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>353.94</v>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>岗位设置
+遗留问题</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="5" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>6、普工</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
+      <c r="D28" s="5" t="n">
+        <v>675.24</v>
+      </c>
+    </row>
+    <row r="29" ht="25" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>退休干部</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="30" ht="25" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>退休工人</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" ht="25" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>离休干部</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="5" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>绩效工资合计</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>乡镇补贴合计</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>15750</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>岗位设置遗留问题</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>张老师</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>岗位设置遗留问题</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>李老师</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>岗位设置遗留问题</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>岗位设置遗留问题合计</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>退休干部</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>退休工人</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32">
+    </row>
+    <row r="32" ht="130" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>离休干部</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>备注：</t>
+          <t>备注：
+退休教师死亡2人：赵明安、候兴志</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="F17:F31"/>
-    <mergeCell ref="E17:E31"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E3:E9"/>
-    <mergeCell ref="F3:F9"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="F11:F19"/>
+  <mergeCells count="32">
+    <mergeCell ref="F20:K20"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="D1:K1"/>
+    <mergeCell ref="E3:E10"/>
     <mergeCell ref="E11:E19"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="F31:K31"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E20:E31"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F19:K19"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="F10:K10"/>
+    <mergeCell ref="F6:K6"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="F7:K7"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F30:K30"/>
+    <mergeCell ref="F15:K15"/>
+    <mergeCell ref="H26:I26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0" firstPageNumber="1"/>

--- a/tp_education_system/backend/exports/绩效工资审批表_2026年5月.xlsx
+++ b/tp_education_system/backend/exports/绩效工资审批表_2026年5月.xlsx
@@ -2,55 +2,421 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22400" windowHeight="9870" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet1'!$A$1:$K$32</definedName>
-  </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;年&quot;m&quot;月&quot;;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+  </numFmts>
+  <fonts count="29">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -59,51 +425,1448 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="00000000"/>
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="41" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="42" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="41" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="43" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="44" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="45" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="141">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="4" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="1" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="7" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="31" fontId="1" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="31" fontId="7" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="50">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 4" xfId="49"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -176,9 +1939,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -186,42 +1949,42 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="WPS">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -250,12 +2013,13 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -284,177 +2048,140 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="WPS">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumOff val="17500"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:hueOff val="-2520000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="phClr">
+                  <a:hueOff val="-4200000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="phClr"/>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="2700000" scaled="1"/>
+          </a:gradFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="phClr">
+                <a:alpha val="60000"/>
+              </a:schemeClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -462,573 +2189,808 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:W32"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.81818181818182" defaultRowHeight="15"/>
   <cols>
-    <col width="13.82" customWidth="1" min="1" max="1"/>
-    <col width="7.64" customWidth="1" min="2" max="2"/>
-    <col width="13.04" customWidth="1" min="3" max="3"/>
-    <col width="9.359999999999999" customWidth="1" min="4" max="4"/>
-    <col width="6.09" customWidth="1" min="5" max="5"/>
-    <col width="8.82" customWidth="1" min="6" max="6"/>
-    <col width="17.64" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="3.91" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="8.640000000000001" customWidth="1" min="11" max="11"/>
+    <col width="13.8181818181818" customWidth="1" style="13" min="1" max="1"/>
+    <col width="7.63636363636364" customWidth="1" style="38" min="2" max="2"/>
+    <col width="13.0363636363636" customWidth="1" style="38" min="3" max="3"/>
+    <col width="9.36363636363636" customWidth="1" style="38" min="4" max="4"/>
+    <col width="6.09090909090909" customWidth="1" style="38" min="5" max="5"/>
+    <col width="8.81818181818182" customWidth="1" style="13" min="6" max="6"/>
+    <col width="17.6363636363636" customWidth="1" style="13" min="7" max="7"/>
+    <col width="5" customWidth="1" style="13" min="8" max="8"/>
+    <col width="3.90909090909091" customWidth="1" style="13" min="9" max="9"/>
+    <col width="11" customWidth="1" style="13" min="10" max="10"/>
+    <col width="8.63636363636364" customWidth="1" style="13" min="11" max="11"/>
+    <col width="8.81818181818182" customWidth="1" style="13" min="12" max="13"/>
+    <col width="10.1818181818182" customWidth="1" style="13" min="14" max="14"/>
+    <col width="15.3636363636364" customWidth="1" style="13" min="15" max="15"/>
+    <col width="11.4545454545455" customWidth="1" style="13" min="16" max="16"/>
+    <col width="8.81818181818182" customWidth="1" style="13" min="17" max="16381"/>
+    <col width="8.81818181818182" customWidth="1" style="3" min="16382" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" customHeight="1">
-      <c r="B1" t="inlineStr">
+    <row r="1" ht="27" customFormat="1" customHeight="1" s="13">
+      <c r="A1" s="4" t="n"/>
+      <c r="B1" s="119" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>2026年5月 义务教育学校教职工绩效工资审批表</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="E1" s="38" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>填报单位：</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="38" t="inlineStr">
         <is>
           <t>太平镇中心学校</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>填报时间:</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="120" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>单位：</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>人、元</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="K2" s="13" t="n"/>
+    </row>
+    <row r="3" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A3" s="121" t="inlineStr">
         <is>
           <t>项  目</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>基础性工资</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="122" t="n"/>
+      <c r="D3" s="123" t="n"/>
+      <c r="E3" s="124" t="inlineStr">
         <is>
           <t>呈报单位意见</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="B4" s="3" t="inlineStr">
+      <c r="F3" s="49" t="n"/>
+      <c r="G3" s="50" t="n"/>
+      <c r="H3" s="50" t="n"/>
+      <c r="I3" s="50" t="n"/>
+      <c r="J3" s="50" t="n"/>
+      <c r="K3" s="51" t="n"/>
+    </row>
+    <row r="4" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A4" s="125" t="n"/>
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>人数</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>月工资标准</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="E4" s="126" t="n"/>
+      <c r="F4" s="41" t="n"/>
+      <c r="K4" s="42" t="n"/>
+    </row>
+    <row r="5" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>行政管理人员</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="126" t="n"/>
+      <c r="F5" s="41" t="n"/>
+      <c r="K5" s="42" t="n"/>
+    </row>
+    <row r="6" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>1、副处级</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="32" t="n">
         <v>3500</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="33" t="n">
         <v>10500</v>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="E6" s="126" t="n"/>
+      <c r="F6" s="127" t="inlineStr">
         <is>
           <t>据实填写，同意呈报。</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="K6" s="128" t="n"/>
+    </row>
+    <row r="7" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>2、正科级</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="32" t="n">
         <v>2800</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="33" t="n">
         <v>14000</v>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="E7" s="126" t="n"/>
+      <c r="F7" s="129" t="inlineStr">
         <is>
           <t>（盖章）</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="K7" s="128" t="n"/>
+    </row>
+    <row r="8" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>3、副科级</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="32" t="n">
         <v>2200</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="33" t="n">
         <v>17600</v>
       </c>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="E8" s="126" t="n"/>
+      <c r="F8" s="41" t="n"/>
+      <c r="K8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>4、科员级</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="40" t="n">
         <v>1185</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="33" t="n">
         <v>5925</v>
       </c>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="E9" s="126" t="n"/>
+      <c r="F9" s="41" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="42" t="n"/>
+    </row>
+    <row r="10" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>5、办事员级</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="23" t="n">
         <v>1106</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="24" t="n">
         <v>2212</v>
       </c>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="E10" s="125" t="n"/>
+      <c r="F10" s="130" t="n">
+        <v>46140</v>
+      </c>
+      <c r="G10" s="131" t="n"/>
+      <c r="H10" s="131" t="n"/>
+      <c r="I10" s="131" t="n"/>
+      <c r="J10" s="131" t="n"/>
+      <c r="K10" s="132" t="n"/>
+    </row>
+    <row r="11" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A11" s="48" t="inlineStr">
         <is>
           <t>专业技术人员</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="124" t="inlineStr">
         <is>
           <t>教育局意见</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="50" t="n"/>
+      <c r="H11" s="50" t="n"/>
+      <c r="I11" s="50" t="n"/>
+      <c r="J11" s="50" t="n"/>
+      <c r="K11" s="51" t="n"/>
+    </row>
+    <row r="12" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>1、正高级</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="40" t="n">
         <v>1862</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="33" t="n">
         <v>3724</v>
       </c>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="E12" s="126" t="n"/>
+      <c r="F12" s="41" t="n"/>
+      <c r="K12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>2、高级教师</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="53" t="n">
         <v>44</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="54" t="n">
         <v>1523</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="55" t="n">
         <v>67012</v>
       </c>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="E13" s="126" t="n"/>
+      <c r="F13" s="41" t="n"/>
+      <c r="K13" s="42" t="n"/>
+      <c r="M13" s="56" t="n"/>
+      <c r="N13" s="56" t="n"/>
+      <c r="O13" s="56" t="n"/>
+      <c r="P13" s="56" t="n"/>
+      <c r="Q13" s="56" t="n"/>
+      <c r="R13" s="56" t="n"/>
+      <c r="S13" s="56" t="n"/>
+      <c r="T13" s="56" t="n"/>
+      <c r="U13" s="56" t="n"/>
+      <c r="V13" s="56" t="n"/>
+      <c r="W13" s="56" t="n"/>
+    </row>
+    <row r="14" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A14" s="57" t="inlineStr">
         <is>
           <t>3、一级教师</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="53" t="n">
         <v>136</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="54" t="n">
         <v>1309</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="55" t="n">
         <v>178024</v>
       </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="E14" s="126" t="n"/>
+      <c r="F14" s="41" t="n"/>
+      <c r="K14" s="42" t="n"/>
+    </row>
+    <row r="15" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A15" s="57" t="inlineStr">
         <is>
           <t>4、二级教师</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="53" t="n">
         <v>150</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="54" t="n">
         <v>1241</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="55" t="n">
         <v>186150</v>
       </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="E15" s="126" t="n"/>
+      <c r="F15" s="129" t="inlineStr">
+        <is>
+          <t>（盖章）</t>
+        </is>
+      </c>
+      <c r="K15" s="128" t="n"/>
+    </row>
+    <row r="16" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>5、三级教师</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="59" t="n">
         <v>19</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="60" t="n">
         <v>1128</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="99" t="n">
         <v>21432</v>
       </c>
-    </row>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="E16" s="126" t="n"/>
+      <c r="F16" s="41" t="n"/>
+      <c r="K16" s="42" t="n"/>
+    </row>
+    <row r="17" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A17" s="62" t="inlineStr">
         <is>
           <t>工人</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B17" s="63" t="n"/>
+      <c r="C17" s="63" t="n"/>
+      <c r="D17" s="64" t="n"/>
+      <c r="E17" s="126" t="n"/>
+      <c r="F17" s="41" t="n"/>
+      <c r="K17" s="42" t="n"/>
+    </row>
+    <row r="18" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A18" s="52" t="inlineStr">
         <is>
           <t>1、高级技师</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="53" t="n">
         <v>1331</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="55" t="n">
         <v>1331</v>
       </c>
-    </row>
-    <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="E18" s="126" t="n"/>
+      <c r="F18" s="41" t="n"/>
+      <c r="K18" s="42" t="n"/>
+    </row>
+    <row r="19" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A19" s="52" t="inlineStr">
         <is>
           <t>2、技师</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="54" t="n">
         <v>1331</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="55" t="n">
         <v>2662</v>
       </c>
-    </row>
-    <row r="20" ht="25" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="E19" s="125" t="n"/>
+      <c r="F19" s="133" t="n">
+        <v>46141</v>
+      </c>
+      <c r="G19" s="131" t="n"/>
+      <c r="H19" s="131" t="n"/>
+      <c r="I19" s="131" t="n"/>
+      <c r="J19" s="131" t="n"/>
+      <c r="K19" s="132" t="n"/>
+    </row>
+    <row r="20" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A20" s="52" t="inlineStr">
         <is>
           <t>3、高级工</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="54" t="n">
         <v>1219</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="55" t="n">
         <v>3657</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="134" t="inlineStr">
         <is>
           <t>人事部门意见</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="135" t="inlineStr">
         <is>
           <t xml:space="preserve">    根据相关文件及有关规定，经审核，同意你单位：</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="G20" s="136" t="n"/>
+      <c r="H20" s="136" t="n"/>
+      <c r="I20" s="136" t="n"/>
+      <c r="J20" s="136" t="n"/>
+      <c r="K20" s="137" t="n"/>
+    </row>
+    <row r="21" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>4、中级工</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="54" t="n">
         <v>1185</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="55" t="n">
         <v>5925</v>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="E21" s="126" t="n"/>
+      <c r="F21" s="73" t="inlineStr">
         <is>
           <t>基础性绩效工资</t>
         </is>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="75" t="n">
         <v>357</v>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="75" t="n">
         <v>462311</v>
       </c>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="K21" s="76" t="inlineStr">
+        <is>
+          <t>元；</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A22" s="52" t="inlineStr">
         <is>
           <t>5、初级工</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="54" t="n">
         <v>1106</v>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="55" t="n">
         <v>1106</v>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="E22" s="126" t="n"/>
+      <c r="F22" s="73" t="inlineStr">
         <is>
           <t>生活补贴</t>
         </is>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="75" t="n">
         <v>356</v>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="75" t="n">
         <v>124600</v>
       </c>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="K22" s="76" t="inlineStr">
+        <is>
+          <t>元；</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A23" s="58" t="inlineStr">
         <is>
           <t>6、普工</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="60" t="n">
         <v>1106</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="E23" s="126" t="n"/>
+      <c r="F23" s="77" t="inlineStr">
         <is>
           <t>合计：</t>
         </is>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="79" t="n">
         <v>586911</v>
       </c>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="K23" s="80" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A24" s="81" t="inlineStr">
         <is>
           <t>绩效工资合计</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="82" t="n">
         <v>357</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="C24" s="82" t="n"/>
+      <c r="D24" s="83" t="n">
         <v>462311</v>
       </c>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="E24" s="126" t="n"/>
+      <c r="F24" s="73" t="inlineStr">
+        <is>
+          <t>岗位设置遗留</t>
+        </is>
+      </c>
+      <c r="H24" s="75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="75" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="J24" s="75" t="n">
+        <v>675.24</v>
+      </c>
+      <c r="K24" s="76" t="inlineStr">
+        <is>
+          <t>元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A25" s="84" t="inlineStr">
         <is>
           <t>乡镇补贴合计</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="85" t="n">
         <v>356</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="85" t="n">
         <v>350</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D25" s="86" t="n">
         <v>124600</v>
       </c>
-    </row>
-    <row r="26" ht="37" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="E25" s="126" t="n"/>
+      <c r="F25" s="77" t="inlineStr">
+        <is>
+          <t>总计：</t>
+        </is>
+      </c>
+      <c r="J25" s="79">
+        <f>J23+J24</f>
+        <v/>
+      </c>
+      <c r="K25" s="80" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="37" customFormat="1" customHeight="1" s="13">
+      <c r="A26" s="87" t="inlineStr">
         <is>
           <t>岗位设置
 遗留问题</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="88" t="inlineStr">
         <is>
           <t>李发金</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="89" t="n">
         <v>321.3</v>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="D26" s="90" t="n">
         <v>321.3</v>
       </c>
-    </row>
-    <row r="27" ht="37" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="E26" s="126" t="n"/>
+      <c r="F26" s="73" t="inlineStr">
+        <is>
+          <t>无乡镇补贴</t>
+        </is>
+      </c>
+      <c r="H26" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="92" t="inlineStr">
+        <is>
+          <t>人：</t>
+        </is>
+      </c>
+      <c r="J26" s="75" t="inlineStr">
+        <is>
+          <t>柯坤</t>
+        </is>
+      </c>
+      <c r="K26" s="76" t="n"/>
+    </row>
+    <row r="27" ht="37" customFormat="1" customHeight="1" s="13">
+      <c r="A27" s="104" t="inlineStr">
         <is>
           <t>岗位设置
 遗留问题</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="94" t="inlineStr">
         <is>
           <t>张照凯</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="105" t="n">
         <v>353.94</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D27" s="96" t="n">
         <v>353.94</v>
       </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="E27" s="126" t="n"/>
+      <c r="F27" s="77" t="n"/>
+      <c r="J27" s="79" t="n"/>
+      <c r="K27" s="80" t="n"/>
+    </row>
+    <row r="28" ht="36" customFormat="1" customHeight="1" s="13">
+      <c r="A28" s="97" t="inlineStr">
         <is>
           <t>岗位设置
 遗留问题</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="98" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="C28" s="59" t="inlineStr"/>
+      <c r="D28" s="99" t="n">
         <v>675.24</v>
       </c>
-    </row>
-    <row r="29" ht="25" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="E28" s="126" t="n"/>
+      <c r="F28" s="41" t="n"/>
+      <c r="K28" s="42" t="n"/>
+    </row>
+    <row r="29" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A29" s="100" t="inlineStr">
         <is>
           <t>退休干部</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="101" t="n">
         <v>447</v>
       </c>
-    </row>
-    <row r="30" ht="25" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="C29" s="102" t="n"/>
+      <c r="D29" s="103" t="n"/>
+      <c r="E29" s="126" t="n"/>
+      <c r="F29" s="41" t="n"/>
+      <c r="K29" s="42" t="n"/>
+    </row>
+    <row r="30" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A30" s="104" t="inlineStr">
         <is>
           <t>退休工人</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="105" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" ht="25" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="106" t="n"/>
+      <c r="E30" s="126" t="n"/>
+      <c r="F30" s="73" t="n"/>
+      <c r="H30" s="75" t="n"/>
+      <c r="I30" s="75" t="n"/>
+      <c r="J30" s="108" t="n"/>
+      <c r="K30" s="128" t="n"/>
+    </row>
+    <row r="31" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A31" s="109" t="inlineStr">
         <is>
           <t>离休干部</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="98" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" ht="130" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="C31" s="59" t="n"/>
+      <c r="D31" s="110" t="n"/>
+      <c r="E31" s="125" t="n"/>
+      <c r="F31" s="138" t="n">
+        <v>46142</v>
+      </c>
+      <c r="G31" s="131" t="n"/>
+      <c r="H31" s="131" t="n"/>
+      <c r="I31" s="131" t="n"/>
+      <c r="J31" s="131" t="n"/>
+      <c r="K31" s="132" t="n"/>
+    </row>
+    <row r="32" ht="130" customFormat="1" customHeight="1" s="13">
+      <c r="A32" s="115" t="inlineStr">
         <is>
           <t>备注：
 退休教师死亡2人：赵明安、候兴志</t>
         </is>
       </c>
+      <c r="B32" s="139" t="n"/>
+      <c r="C32" s="139" t="n"/>
+      <c r="D32" s="139" t="n"/>
+      <c r="E32" s="139" t="n"/>
+      <c r="F32" s="139" t="n"/>
+      <c r="G32" s="139" t="n"/>
+      <c r="H32" s="139" t="n"/>
+      <c r="I32" s="139" t="n"/>
+      <c r="J32" s="139" t="n"/>
+      <c r="K32" s="140" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="26">
     <mergeCell ref="F20:K20"/>
     <mergeCell ref="F27:I27"/>
-    <mergeCell ref="D1:K1"/>
     <mergeCell ref="E3:E10"/>
     <mergeCell ref="E11:E19"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J30:K30"/>
     <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="F31:K31"/>
     <mergeCell ref="F25:I25"/>
@@ -1037,24 +2999,18 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="J25:K25"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="A32:K32"/>
-    <mergeCell ref="J22:K22"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F19:K19"/>
-    <mergeCell ref="J21:K21"/>
     <mergeCell ref="F10:K10"/>
     <mergeCell ref="F6:K6"/>
-    <mergeCell ref="H24:I24"/>
     <mergeCell ref="F7:K7"/>
-    <mergeCell ref="J23:K23"/>
     <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F30:K30"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="F15:K15"/>
-    <mergeCell ref="H26:I26"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0" firstPageNumber="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="76"/>
 </worksheet>
 </file>
--- a/tp_education_system/backend/exports/绩效工资审批表_2026年5月.xlsx
+++ b/tp_education_system/backend/exports/绩效工资审批表_2026年5月.xlsx
@@ -2330,15 +2330,9 @@
           <t>1、副处级</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D6" s="33" t="n">
-        <v>10500</v>
-      </c>
+      <c r="B6" s="32" t="inlineStr"/>
+      <c r="C6" s="32" t="inlineStr"/>
+      <c r="D6" s="33" t="inlineStr"/>
       <c r="E6" s="126" t="n"/>
       <c r="F6" s="127" t="inlineStr">
         <is>
@@ -2353,15 +2347,9 @@
           <t>2、正科级</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>2800</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>14000</v>
-      </c>
+      <c r="B7" s="32" t="inlineStr"/>
+      <c r="C7" s="32" t="inlineStr"/>
+      <c r="D7" s="33" t="inlineStr"/>
       <c r="E7" s="126" t="n"/>
       <c r="F7" s="129" t="inlineStr">
         <is>
@@ -2376,15 +2364,9 @@
           <t>3、副科级</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>2200</v>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>17600</v>
-      </c>
+      <c r="B8" s="32" t="inlineStr"/>
+      <c r="C8" s="32" t="inlineStr"/>
+      <c r="D8" s="33" t="inlineStr"/>
       <c r="E8" s="126" t="n"/>
       <c r="F8" s="41" t="n"/>
       <c r="K8" s="42" t="n"/>
@@ -2395,15 +2377,9 @@
           <t>4、科员级</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="40" t="n">
-        <v>1185</v>
-      </c>
-      <c r="D9" s="33" t="n">
-        <v>5925</v>
-      </c>
+      <c r="B9" s="32" t="inlineStr"/>
+      <c r="C9" s="40" t="inlineStr"/>
+      <c r="D9" s="33" t="inlineStr"/>
       <c r="E9" s="126" t="n"/>
       <c r="F9" s="41" t="n"/>
       <c r="G9" s="13" t="n"/>
@@ -2418,15 +2394,9 @@
           <t>5、办事员级</t>
         </is>
       </c>
-      <c r="B10" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="23" t="n">
-        <v>1106</v>
-      </c>
-      <c r="D10" s="24" t="n">
-        <v>2212</v>
-      </c>
+      <c r="B10" s="23" t="inlineStr"/>
+      <c r="C10" s="23" t="inlineStr"/>
+      <c r="D10" s="24" t="inlineStr"/>
       <c r="E10" s="125" t="n"/>
       <c r="F10" s="130" t="n">
         <v>46140</v>
@@ -2464,15 +2434,9 @@
           <t>1、正高级</t>
         </is>
       </c>
-      <c r="B12" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="40" t="n">
-        <v>1862</v>
-      </c>
-      <c r="D12" s="33" t="n">
-        <v>3724</v>
-      </c>
+      <c r="B12" s="32" t="inlineStr"/>
+      <c r="C12" s="40" t="inlineStr"/>
+      <c r="D12" s="33" t="inlineStr"/>
       <c r="E12" s="126" t="n"/>
       <c r="F12" s="41" t="n"/>
       <c r="K12" s="42" t="n"/>
@@ -2483,15 +2447,9 @@
           <t>2、高级教师</t>
         </is>
       </c>
-      <c r="B13" s="53" t="n">
-        <v>44</v>
-      </c>
-      <c r="C13" s="54" t="n">
-        <v>1523</v>
-      </c>
-      <c r="D13" s="55" t="n">
-        <v>67012</v>
-      </c>
+      <c r="B13" s="53" t="inlineStr"/>
+      <c r="C13" s="54" t="inlineStr"/>
+      <c r="D13" s="55" t="inlineStr"/>
       <c r="E13" s="126" t="n"/>
       <c r="F13" s="41" t="n"/>
       <c r="K13" s="42" t="n"/>
@@ -2513,15 +2471,9 @@
           <t>3、一级教师</t>
         </is>
       </c>
-      <c r="B14" s="53" t="n">
-        <v>136</v>
-      </c>
-      <c r="C14" s="54" t="n">
-        <v>1309</v>
-      </c>
-      <c r="D14" s="55" t="n">
-        <v>178024</v>
-      </c>
+      <c r="B14" s="53" t="inlineStr"/>
+      <c r="C14" s="54" t="inlineStr"/>
+      <c r="D14" s="55" t="inlineStr"/>
       <c r="E14" s="126" t="n"/>
       <c r="F14" s="41" t="n"/>
       <c r="K14" s="42" t="n"/>
@@ -2532,15 +2484,9 @@
           <t>4、二级教师</t>
         </is>
       </c>
-      <c r="B15" s="53" t="n">
-        <v>150</v>
-      </c>
-      <c r="C15" s="54" t="n">
-        <v>1241</v>
-      </c>
-      <c r="D15" s="55" t="n">
-        <v>186150</v>
-      </c>
+      <c r="B15" s="53" t="inlineStr"/>
+      <c r="C15" s="54" t="inlineStr"/>
+      <c r="D15" s="55" t="inlineStr"/>
       <c r="E15" s="126" t="n"/>
       <c r="F15" s="129" t="inlineStr">
         <is>
@@ -2555,15 +2501,9 @@
           <t>5、三级教师</t>
         </is>
       </c>
-      <c r="B16" s="59" t="n">
-        <v>19</v>
-      </c>
-      <c r="C16" s="60" t="n">
-        <v>1128</v>
-      </c>
-      <c r="D16" s="99" t="n">
-        <v>21432</v>
-      </c>
+      <c r="B16" s="59" t="inlineStr"/>
+      <c r="C16" s="60" t="inlineStr"/>
+      <c r="D16" s="99" t="inlineStr"/>
       <c r="E16" s="126" t="n"/>
       <c r="F16" s="41" t="n"/>
       <c r="K16" s="42" t="n"/>
@@ -2587,15 +2527,9 @@
           <t>1、高级技师</t>
         </is>
       </c>
-      <c r="B18" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="53" t="n">
-        <v>1331</v>
-      </c>
-      <c r="D18" s="55" t="n">
-        <v>1331</v>
-      </c>
+      <c r="B18" s="53" t="inlineStr"/>
+      <c r="C18" s="53" t="inlineStr"/>
+      <c r="D18" s="55" t="inlineStr"/>
       <c r="E18" s="126" t="n"/>
       <c r="F18" s="41" t="n"/>
       <c r="K18" s="42" t="n"/>
@@ -2606,15 +2540,9 @@
           <t>2、技师</t>
         </is>
       </c>
-      <c r="B19" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" s="54" t="n">
-        <v>1331</v>
-      </c>
-      <c r="D19" s="55" t="n">
-        <v>2662</v>
-      </c>
+      <c r="B19" s="53" t="inlineStr"/>
+      <c r="C19" s="54" t="inlineStr"/>
+      <c r="D19" s="55" t="inlineStr"/>
       <c r="E19" s="125" t="n"/>
       <c r="F19" s="133" t="n">
         <v>46141</v>
@@ -2631,15 +2559,9 @@
           <t>3、高级工</t>
         </is>
       </c>
-      <c r="B20" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" s="54" t="n">
-        <v>1219</v>
-      </c>
-      <c r="D20" s="55" t="n">
-        <v>3657</v>
-      </c>
+      <c r="B20" s="53" t="inlineStr"/>
+      <c r="C20" s="54" t="inlineStr"/>
+      <c r="D20" s="55" t="inlineStr"/>
       <c r="E20" s="134" t="inlineStr">
         <is>
           <t>人事部门意见</t>
@@ -2662,15 +2584,9 @@
           <t>4、中级工</t>
         </is>
       </c>
-      <c r="B21" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="C21" s="54" t="n">
-        <v>1185</v>
-      </c>
-      <c r="D21" s="55" t="n">
-        <v>5925</v>
-      </c>
+      <c r="B21" s="53" t="inlineStr"/>
+      <c r="C21" s="54" t="inlineStr"/>
+      <c r="D21" s="55" t="inlineStr"/>
       <c r="E21" s="126" t="n"/>
       <c r="F21" s="73" t="inlineStr">
         <is>
@@ -2700,15 +2616,9 @@
           <t>5、初级工</t>
         </is>
       </c>
-      <c r="B22" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="54" t="n">
-        <v>1106</v>
-      </c>
-      <c r="D22" s="55" t="n">
-        <v>1106</v>
-      </c>
+      <c r="B22" s="53" t="inlineStr"/>
+      <c r="C22" s="54" t="inlineStr"/>
+      <c r="D22" s="55" t="inlineStr"/>
       <c r="E22" s="126" t="n"/>
       <c r="F22" s="73" t="inlineStr">
         <is>
@@ -2738,15 +2648,9 @@
           <t>6、普工</t>
         </is>
       </c>
-      <c r="B23" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="60" t="n">
-        <v>1106</v>
-      </c>
-      <c r="D23" s="99" t="n">
-        <v>0</v>
-      </c>
+      <c r="B23" s="59" t="inlineStr"/>
+      <c r="C23" s="60" t="inlineStr"/>
+      <c r="D23" s="99" t="inlineStr"/>
       <c r="E23" s="126" t="n"/>
       <c r="F23" s="77" t="inlineStr">
         <is>
@@ -2836,17 +2740,9 @@
 遗留问题</t>
         </is>
       </c>
-      <c r="B26" s="88" t="inlineStr">
-        <is>
-          <t>李发金</t>
-        </is>
-      </c>
-      <c r="C26" s="89" t="n">
-        <v>321.3</v>
-      </c>
-      <c r="D26" s="90" t="n">
-        <v>321.3</v>
-      </c>
+      <c r="B26" s="88" t="inlineStr"/>
+      <c r="C26" s="89" t="inlineStr"/>
+      <c r="D26" s="90" t="inlineStr"/>
       <c r="E26" s="126" t="n"/>
       <c r="F26" s="73" t="inlineStr">
         <is>
@@ -2875,17 +2771,9 @@
 遗留问题</t>
         </is>
       </c>
-      <c r="B27" s="94" t="inlineStr">
-        <is>
-          <t>张照凯</t>
-        </is>
-      </c>
-      <c r="C27" s="105" t="n">
-        <v>353.94</v>
-      </c>
-      <c r="D27" s="96" t="n">
-        <v>353.94</v>
-      </c>
+      <c r="B27" s="94" t="inlineStr"/>
+      <c r="C27" s="105" t="inlineStr"/>
+      <c r="D27" s="96" t="inlineStr"/>
       <c r="E27" s="126" t="n"/>
       <c r="F27" s="77" t="n"/>
       <c r="J27" s="79" t="n"/>
@@ -2898,13 +2786,9 @@
 遗留问题</t>
         </is>
       </c>
-      <c r="B28" s="98" t="n">
-        <v>2</v>
-      </c>
+      <c r="B28" s="98" t="inlineStr"/>
       <c r="C28" s="59" t="inlineStr"/>
-      <c r="D28" s="99" t="n">
-        <v>675.24</v>
-      </c>
+      <c r="D28" s="99" t="inlineStr"/>
       <c r="E28" s="126" t="n"/>
       <c r="F28" s="41" t="n"/>
       <c r="K28" s="42" t="n"/>
